--- a/feasibility-analysis/feasibility-analysis-yaoan.xlsx
+++ b/feasibility-analysis/feasibility-analysis-yaoan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubSource\Graduation-Project\feasibility-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A89172-FDE7-45F2-AEF6-A467ABA22ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153DC40F-2639-4B6A-8568-068BB06FC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C524DE1E-122D-431B-9986-3C54448ABE0B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
   <si>
     <t>挑戰</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,13 +209,86 @@
   <si>
     <t>基於Fabric.js設計的繪畫筆刷，有特別的筆刷</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尋找生成藝術作品的AI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>進行中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepAI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以呼叫API使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有免費的API額度能用，暫時無法測試</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網頁測試，有額度限制，圖解析度不高，不能理解中文。有圖片、影片、音樂Generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://deepai.org/machine-learning-model/text2img</t>
+  </si>
+  <si>
+    <t>DALLE-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網頁測試，有額度限制，可以很精確地接收指令，圖片精美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Midjourney</t>
+  </si>
+  <si>
+    <t>沒有API，通常都是透過DC和網頁來使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未測試任何版本。生成的圖品質挺高，風格多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepDream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有API，只能透過TensorFlow或PyTorch來自己實作，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未測試任何版本。該技術生成出的圖片有一種迷幻感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion</t>
+  </si>
+  <si>
+    <t>有多個平台的API能用，尚未測試</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網頁測試，有額度限制，提示詞僅支援英文，生成的圖片精緻，但有時會出現很誇張的bug
+紀錄：Hugging Face、Replicate、WizMode、ModelsLab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 生成藝術</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -237,6 +310,14 @@
       <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -266,7 +347,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -276,14 +357,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -600,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B475F2AA-3FCA-4F58-9686-F51A56C544F1}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -617,7 +708,7 @@
     <col min="12" max="12" width="90" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,23 +746,23 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="7">
         <v>45572</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="7">
         <v>45574</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -693,13 +784,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
@@ -715,15 +806,15 @@
       <c r="K3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
@@ -739,15 +830,15 @@
       <c r="K4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
@@ -763,15 +854,15 @@
       <c r="K5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="1" t="s">
         <v>27</v>
       </c>
@@ -787,15 +878,15 @@
       <c r="K6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="1" t="s">
         <v>28</v>
       </c>
@@ -811,15 +902,15 @@
       <c r="K7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
@@ -835,9 +926,9 @@
       <c r="K8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -851,14 +942,157 @@
       <c r="K9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7">
+        <v>45576</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" spans="1:16" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="1"/>
+      <c r="G15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="12">
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C11:C15"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="E11:E15"/>
     <mergeCell ref="L2:L9"/>
     <mergeCell ref="F2:F8"/>
     <mergeCell ref="A2:A8"/>
